--- a/sources/anna_step10.xlsx
+++ b/sources/anna_step10.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD136"/>
+  <dimension ref="A1:AD134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col hidden="1" min="5" max="5"/>
     <col width="68" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -436,9 +436,9 @@
     <col width="19" customWidth="1" min="14" max="14"/>
     <col hidden="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
     <col hidden="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
     <col hidden="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
@@ -3718,12 +3718,12 @@
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>df+1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>df+1 ,2</t>
+          <t>1 ,2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3743,22 +3743,22 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>+1 +1</t>
+          <t>+1 -5</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+1 +1</t>
+          <t>+1 -5</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3783,1107 +3783,1072 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>4,10</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>4,10</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>d0c5a7da-b497-4286-a857-fd8930564a52</t>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>38c084ac-b201-4176-b5c8-6332f4f011fb</t>
+          <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
+          <t>– 3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1 ,2 ,3</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>– Low Kick</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Double Punch – Low Kick</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1 1 1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>+1 -5</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>+7 +7</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>+7 +7</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>4,10,10</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>hhl</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Does not work starting with d/f+1,2</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>fefdb095-541f-4d3e-939a-f3c64b7764d5</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>c924ef1d-a211-4681-b97f-c72dcfadc034</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>– 4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1 ,2 ,4</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>– Bermuda Triangle</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Double Punch – Bermuda Triangle</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1 1 1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>-19</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>+1 -5 -19</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>+7 +7 KD</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>+7 +7 KD</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4,10,15</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>hhh</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>02cdaf34-b75f-4d9e-8eb0-6c4fa1d43d20</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>7bdd8152-f754-413b-93c7-6a475498cf57</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>– 1,4,2 [~U_~D]</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1 ,2 ,1 ,4 ,2 [~U_~D]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>– Snake [SS]</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Double Punch – Snake [SS]</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>+1 0 +2</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>+1 -5 +1 0 +2</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>+12 -2 0</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>+7 +7 +12 -2 0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>+12 -2 0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>+7 +7 +12 -2 0</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>6,15,12</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>4,10,6,15,12</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>hhh</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>hhhhh</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>–– 3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1 ,2 ,1 ,4 ,2 [~U_~D],3</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>–– High Kick</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Double Punch – Snake [SS] – High Kick</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>+1 -5 +1 0 +2 0</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>+9</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>+7 +7 +12 -2 0 +9</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>+9</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>+7 +7 +12 -2 0 +9</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>4,10,6,15,12,17</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>hhhhhh</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>d0568b44-b953-4c64-af12-551ed65bde27</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>e48f0a78-2da9-48e4-8d2d-3e422a9029c9</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>–– uf+3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1 ,2 ,1 ,4 ,2 [~U_~D],uf+3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>–– Bone Cutter</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Double Punch – Snake [SS] – Bone Cutter</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>+1 -5 +1 0 +2</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>+7 +7 +12 -2 0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>+7 +7 +12 -2 0</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>13,10,10</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>4,10,6,15,12,13,10,10</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>hhhhhh</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>be54fc7b-95ac-42d4-b8b3-fcb452c8baa5</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>07611425-29b3-41ef-8a3f-0717f290a07d</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>–– 4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1 ,2 ,1 ,4 ,2 [~U_~D],4</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>–– Spin Trip</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Double Punch – Snake [SS] – Spin Trip</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>-23</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>+1 -5 +1 0 +2 -23</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>+7 +7 +12 -2 0 KD</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>+7 +7 +12 -2 0 KD</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>4,10,6,15,12,21</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>hhhhhL</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>caa2d86d-5b50-4cdf-9692-4d547308f93b</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>166cad2e-2c08-4739-b7e4-1e2d60f6a73b</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>– 1,b+4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1 ,2 ,1 ,b+4</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>– Jab Rush - Low Kick</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Double Punch – Jab Rush - Low Kick</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1 1 1 1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>+1 -10</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>+1 -5 +1 -10</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>+12 +1</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>+7 +7 +12 +1</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>+12 +1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>+7 +7 +12 +1</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>6,8</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>4,10,6,8</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>hl</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>hhhl</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>1b40f311-91f7-4a46-be3b-81978d302f90</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>b301db8a-cbb4-4227-a630-d5ca1ba4fe0e</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1 ,4</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PDK Combo</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>PDK Combo</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>+1 -10</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>+1 -10</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>+7 +1</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>+7 +1</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>+7 +1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>+7 +1</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>hl</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>hl</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>3db16d2c-f04e-40cb-a74c-ecbfde854d6d</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>eb2690e4-5fed-4120-8ae5-c870948f502d</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>df+1,2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>df+1 ,2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Double Punch</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Double Punch</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>+1 +1</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>+1 +1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>+7 +7</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>+7 +7</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>+7 +7</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>+7 +7</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>10,15</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>10,15</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>mh</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>mh</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>d0c5a7da-b497-4286-a857-fd8930564a52</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>38c084ac-b201-4176-b5c8-6332f4f011fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>1 ,2</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BT 2,2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>+1 -5</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>+1 -5</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>+7 +7</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>+7 +7</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>+7 +7</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>+7 +7</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>4,10</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>4,10</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>-8 -5</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-8 -5</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>+3 +7</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>+3 +7</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>+3 +7</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>+3 +7</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>15,10</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>15,10</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1 ,2</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>BT 2,2</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Double Punch</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Double Punch</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>1 1</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>-8 -5</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>-8 -5</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>+3 +7</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>+3 +7</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>+3 +7</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>+3 +7</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>15,10</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>15,10</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>hh</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>hh</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>– 3</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1 ,2 ,3</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>– Low Kick</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Double Punch – Low Kick</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>1 1 1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>-8 -5</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>+3 +7</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>+3 +7</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>15,10,10</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>hhl</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Does not work starting with d/f+1,2</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>fefdb095-541f-4d3e-939a-f3c64b7764d5</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>c924ef1d-a211-4681-b97f-c72dcfadc034</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>– 4</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1 ,2 ,4</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>– Bermuda Triangle</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Double Punch – Bermuda Triangle</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>1 1 1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>-19</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>-8 -5 -19</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>+3 +7 KD</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>+3 +7 KD</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>15,10,15</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>hhh</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>02cdaf34-b75f-4d9e-8eb0-6c4fa1d43d20</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>7bdd8152-f754-413b-93c7-6a475498cf57</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>– 1,4,2 [~U_~D]</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1 ,2 ,1 ,4 ,2 [~U_~D]</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>– Snake [SS]</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Double Punch – Snake [SS]</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>1 1 1 1 1 0</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>+1 0 +2</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>-8 -5 +1 0 +2</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>+12 -2 0</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>+3 +7 +12 -2 0</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>+12 -2 0</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>+3 +7 +12 -2 0</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>6,15,12</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>15,10,6,15,12</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>hhh</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>hhhhh</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>–– 3</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1 ,2 ,1 ,4 ,2 [~U_~D],3</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>–– High Kick</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Double Punch – Snake [SS] – High Kick</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>1 1 1 1 1 1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>-8 -5 +1 0 +2 0</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>+3 +7 +12 -2 0 +9</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>+3 +7 +12 -2 0 +9</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>15,10,6,15,12,17</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>hhhhhh</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>d0568b44-b953-4c64-af12-551ed65bde27</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>e48f0a78-2da9-48e4-8d2d-3e422a9029c9</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>–– uf+3</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1 ,2 ,1 ,4 ,2 [~U_~D],uf+3</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>–– Bone Cutter</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Double Punch – Snake [SS] – Bone Cutter</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>1 1 1 1 1 1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>-8 -5 +1 0 +2</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>+3 +7 +12 -2 0</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>+3 +7 +12 -2 0</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>13,10,10</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>15,10,6,15,12,13,10,10</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>hhhhhh</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>be54fc7b-95ac-42d4-b8b3-fcb452c8baa5</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>07611425-29b3-41ef-8a3f-0717f290a07d</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>–– 4</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1 ,2 ,1 ,4 ,2 [~U_~D],4</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>–– Spin Trip</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Double Punch – Snake [SS] – Spin Trip</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>1 1 1 1 1 1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>-23</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>-8 -5 +1 0 +2 -23</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>+3 +7 +12 -2 0 KD</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>+3 +7 +12 -2 0 KD</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>15,10,6,15,12,21</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>hhhhhL</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>caa2d86d-5b50-4cdf-9692-4d547308f93b</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>166cad2e-2c08-4739-b7e4-1e2d60f6a73b</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>– 1,b+4</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1 ,2 ,1 ,b+4</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>– Jab Rush - Low Kick</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Double Punch – Jab Rush - Low Kick</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>1 1 1 1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>+1 -10</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>-8 -5 +1 -10</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>+12 +1</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>+3 +7 +12 +1</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>+12 +1</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>+3 +7 +12 +1</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>6,8</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>15,10,6,8</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>hl</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>hhhl</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>1b40f311-91f7-4a46-be3b-81978d302f90</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>b301db8a-cbb4-4227-a630-d5ca1ba4fe0e</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1 ,4</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>PDK Combo</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>PDK Combo</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>1 1</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>+1 -10</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>+1 -10</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>+7 +1</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>+7 +1</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>+7 +1</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>+7 +1</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>4,8</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>4,8</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>hl</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>hl</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>3db16d2c-f04e-40cb-a74c-ecbfde854d6d</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>eb2690e4-5fed-4120-8ae5-c870948f502d</t>
         </is>
       </c>
     </row>
@@ -11558,11 +11523,6 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB123" t="inlineStr">
         <is>
           <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
@@ -11625,11 +11585,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB124" t="inlineStr">
         <is>
           <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
@@ -11692,11 +11647,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB125" t="inlineStr">
         <is>
           <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
@@ -11759,11 +11709,6 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB126" t="inlineStr">
         <is>
           <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
@@ -11826,11 +11771,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB127" t="inlineStr">
         <is>
           <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
@@ -11893,11 +11833,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB128" t="inlineStr">
         <is>
           <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
@@ -11960,11 +11895,6 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB129" t="inlineStr">
         <is>
           <t>93714c88-336b-411f-b863-f65c2a39733a</t>
@@ -12025,11 +11955,6 @@
       <c r="W130" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
@@ -12255,120 +12180,6 @@
         </is>
       </c>
       <c r="AD134" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>df+1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>df+1 ,2 ,1 ,2 ,3 ,3 ,2 ,1 ,2 ,4</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>1 1 1 1 1 1 1 1 1 1</t>
-        </is>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>10,15,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>10,15,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>mhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>mhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>3868d410-2e89-48d9-953a-b6d47bab49c4</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>1 ,2 ,1 ,2 ,3 ,3 ,2 ,1 ,2 ,4</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>1 1 1 1 1 1 1 1 1 1</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>15,10,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>15,10,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>hhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>hhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>2f43bade-2f95-4531-9ea3-4cdbb2bdd0bd</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/anna_step10.xlsx
+++ b/sources/anna_step10.xlsx
@@ -426,7 +426,7 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col hidden="1" min="5" max="5"/>
     <col width="68" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col hidden="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -4019,27 +4019,32 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>– 1,4,2 [~U_~D]</t>
+          <t>– 1,4,2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1 ,2 ,1 ,4 ,2 [~U_~D]</t>
+          <t>1 ,2 ,1 ,4 ,2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>– Snake [SS]</t>
+          <t>– Snake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS]</t>
+          <t>Double Punch – Snake</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1 1 1 1 1 0</t>
+          <t>1 1 1 1 1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4131,7 +4136,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1 ,2 ,1 ,4 ,2 [~U_~D],3</t>
+          <t>1 ,2 ,1 ,4 ,2 ,3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4141,7 +4146,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – High Kick</t>
+          <t>Double Punch – Snake – High Kick</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4238,7 +4243,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1 ,2 ,1 ,4 ,2 [~U_~D],uf+3</t>
+          <t>1 ,2 ,1 ,4 ,2 ,uf+3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4248,7 +4253,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – Bone Cutter</t>
+          <t>Double Punch – Snake – Bone Cutter</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4325,7 +4330,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1 ,2 ,1 ,4 ,2 [~U_~D],4</t>
+          <t>1 ,2 ,1 ,4 ,2 ,4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4335,7 +4340,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – Spin Trip</t>
+          <t>Double Punch – Snake – Spin Trip</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -8067,27 +8072,32 @@
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t>– 4&lt;2 [~U_~D]</t>
+          <t>– 4&lt;2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>df+3 ,1 ,4 &lt;2 [~U_~D]</t>
+          <t>df+3 ,1 ,4 &lt;2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>– Snake [SS]</t>
+          <t>– Snake</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Assault – Snake [SS]</t>
+          <t>Assault – Snake</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1 1 1 1 0</t>
+          <t>1 1 1 1</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8179,7 +8189,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>df+3 ,1 ,4 &lt;2 [~U_~D],3</t>
+          <t>df+3 ,1 ,4 &lt;2 ,3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8189,7 +8199,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Assault – Snake [SS] – High Kick</t>
+          <t>Assault – Snake – High Kick</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8281,7 +8291,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>df+3 ,1 ,4 &lt;2 [~U_~D],uf+3</t>
+          <t>df+3 ,1 ,4 &lt;2 ,uf+3</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8291,7 +8301,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Assault – Snake [SS] – Bone Cutter</t>
+          <t>Assault – Snake – Bone Cutter</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8368,7 +8378,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>df+3 ,1 ,4 &lt;2 [~U_~D],4</t>
+          <t>df+3 ,1 ,4 &lt;2 ,4</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8378,7 +8388,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Assault – Snake [SS] – Spin Trip</t>
+          <t>Assault – Snake – Spin Trip</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8572,27 +8582,32 @@
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]</t>
+          <t>df+3,2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D]</t>
+          <t>df+3 ,2</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS]</t>
+          <t>Creeping Snake</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS]</t>
+          <t>Creeping Snake</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1 1 0</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8679,7 +8694,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],1 ,4</t>
+          <t>df+3 ,2 ,1 ,4</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8689,7 +8704,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS] – Biting Snake</t>
+          <t>Creeping Snake – Biting Snake</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8786,7 +8801,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],3</t>
+          <t>df+3 ,2 ,3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8796,7 +8811,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS] – High Kick</t>
+          <t>Creeping Snake – High Kick</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8893,7 +8908,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],d+3</t>
+          <t>df+3 ,2 ,d+3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8903,7 +8918,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS] – Low Kick</t>
+          <t>Creeping Snake – Low Kick</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9000,7 +9015,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],4</t>
+          <t>df+3 ,2 ,4</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9010,7 +9025,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS] – Roundhouse</t>
+          <t>Creeping Snake – Roundhouse</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9226,27 +9241,32 @@
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>–– 4&lt;2 [~U_~D]</t>
+          <t>–– 4&lt;2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>df+3 ,3 ,3 ,1 ,4 &lt;2 [~U_~D]</t>
+          <t>df+3 ,3 ,3 ,1 ,4 &lt;2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>–– Snake [SS]</t>
+          <t>–– Snake</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spike Combo – Assault – Snake [SS]</t>
+          <t>Spike Combo – Assault – Snake</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1 1 1 1 1 1 0</t>
+          <t>1 1 1 1 1 1</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -9303,7 +9323,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>df+3 ,3 ,3 ,1 ,4 &lt;2 [~U_~D],3</t>
+          <t>df+3 ,3 ,3 ,1 ,4 &lt;2 ,3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9313,7 +9333,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spike Combo – Assault – Snake [SS] – High Kick</t>
+          <t>Spike Combo – Assault – Snake – High Kick</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9370,7 +9390,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>df+3 ,3 ,3 ,1 ,4 &lt;2 [~U_~D],uf+3</t>
+          <t>df+3 ,3 ,3 ,1 ,4 &lt;2 ,uf+3</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9380,7 +9400,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spike Combo – Assault – Snake [SS] – Bone Cutter</t>
+          <t>Spike Combo – Assault – Snake – Bone Cutter</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9437,7 +9457,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>df+3 ,3 ,3 ,1 ,4 &lt;2 [~U_~D],4</t>
+          <t>df+3 ,3 ,3 ,1 ,4 &lt;2 ,4</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9447,7 +9467,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spike Combo – Assault – Snake [SS] – Spin Trip</t>
+          <t>Spike Combo – Assault – Snake – Spin Trip</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9745,27 +9765,32 @@
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>uf+4,3,4 [~U_~D]</t>
+          <t>uf+4,3,4</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>uf+4 ,3 ,4 [~U_~D]</t>
+          <t>uf+4 ,3 ,4</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Can Opener [SS]</t>
+          <t>Can Opener</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Can Opener [SS]</t>
+          <t>Can Opener</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1 1 1 0</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9852,27 +9877,32 @@
     <row r="103">
       <c r="B103" t="inlineStr">
         <is>
-          <t>d+4&lt;1 [~U_~D]</t>
+          <t>d+4&lt;1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>d+4 &lt;1 [~U_~D]</t>
+          <t>d+4 &lt;1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1 1 0</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9959,27 +9989,32 @@
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t>FC+4,1 [~U_~D]</t>
+          <t>FC+4,1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FC+4 ,1 [~U_~D]</t>
+          <t>FC+4 ,1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1 1 0</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">

--- a/sources/anna_step10.xlsx
+++ b/sources/anna_step10.xlsx
@@ -1042,6 +1042,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>d0af4541-7b9a-41bf-9ff0-5f2b5d4a1a13</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>d0af4541-7b9a-41bf-9ff0-5f2b5d4a1a13</t>
@@ -1109,6 +1114,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1bd5e4f8-ba3c-42b7-8668-d0aacd0a7412</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
           <t>1bd5e4f8-ba3c-42b7-8668-d0aacd0a7412</t>
@@ -1174,6 +1184,11 @@
       <c r="W10" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>31ad5619-ed1a-41f7-95e0-e44eadc9aed1</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -11501,6 +11516,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
+        </is>
+      </c>
       <c r="AB122" t="inlineStr">
         <is>
           <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
@@ -11558,6 +11578,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
+        </is>
+      </c>
       <c r="AB123" t="inlineStr">
         <is>
           <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
@@ -11620,6 +11645,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
+        </is>
+      </c>
       <c r="AB124" t="inlineStr">
         <is>
           <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
@@ -11682,6 +11712,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
+        </is>
+      </c>
       <c r="AB125" t="inlineStr">
         <is>
           <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
@@ -11744,6 +11779,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
+        </is>
+      </c>
       <c r="AB126" t="inlineStr">
         <is>
           <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
@@ -11806,6 +11846,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
+        </is>
+      </c>
       <c r="AB127" t="inlineStr">
         <is>
           <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
@@ -11868,6 +11913,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
+        </is>
+      </c>
       <c r="AB128" t="inlineStr">
         <is>
           <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
@@ -11930,6 +11980,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>93714c88-336b-411f-b863-f65c2a39733a</t>
+        </is>
+      </c>
       <c r="AB129" t="inlineStr">
         <is>
           <t>93714c88-336b-411f-b863-f65c2a39733a</t>
@@ -11990,6 +12045,11 @@
       <c r="W130" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>0e938de5-6095-4002-9ade-581f69b50247</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
@@ -12207,6 +12267,11 @@
       <c r="U134" t="inlineStr">
         <is>
           <t>hhhhhlhhhh</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>d61c2d77-39a1-494e-8996-5a62586356a9</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
